--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_14-04-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_14-04-2026.xlsx
@@ -533,17 +533,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£12.76</t>
+          <t>£12.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£12.76</t>
+          <t>£12.33</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£12.76</t>
+          <t>£12.33</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£13.49</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -625,17 +625,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£14.51</t>
+          <t>£14.06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£14.51</t>
+          <t>£14.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£14.51</t>
+          <t>£14.06</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -717,12 +717,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£18.51</t>
+          <t>£18.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£18.51</t>
+          <t>£18.33</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>£17.17</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£18.92</t>
+          <t>£18.44</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£18.92</t>
+          <t>£18.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£18.92</t>
+          <t>£18.44</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£23.91</t>
+          <t>£23.65</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£23.91</t>
+          <t>£23.65</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£23.91</t>
+          <t>£23.65</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£30.70</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£30.90</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£38.75</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£58.12</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£41.52</t>
+          <t>£38.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£41.52</t>
+          <t>£38.76</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£40.49</t>
+          <t>£40.15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£40.49</t>
+          <t>£40.15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£40.49</t>
+          <t>£40.15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£49.75</t>
+          <t>£47.85</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£49.75</t>
+          <t>£47.85</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£49.76</t>
+          <t>£49.00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£49.76</t>
+          <t>£49.00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£40.47</t>
+          <t>£40.14</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>£40.47</t>
+          <t>£40.14</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
